--- a/elite-data/manifest-templates/EL_template_StudyFolderTemplate.xlsx
+++ b/elite-data/manifest-templates/EL_template_StudyFolderTemplate.xlsx
@@ -269,7 +269,7 @@
     <t>Not assigned</t>
   </si>
   <si>
-    <t>False</t>
+    <t>false</t>
   </si>
   <si>
     <t>10x multiome</t>

--- a/elite-data/manifest-templates/EL_template_StudyFolderTemplate.xlsx
+++ b/elite-data/manifest-templates/EL_template_StudyFolderTemplate.xlsx
@@ -314,7 +314,7 @@
     <t>Human</t>
   </si>
   <si>
-    <t>Not applicable</t>
+    <t>not applicable</t>
   </si>
   <si>
     <t>U19AG023122</t>
@@ -341,7 +341,7 @@
     <t>Mouse</t>
   </si>
   <si>
-    <t>Not collected</t>
+    <t>not collected</t>
   </si>
   <si>
     <t>U19AG063893</t>
@@ -470,7 +470,7 @@
     <t>cerebral cortex</t>
   </si>
   <si>
-    <t>Unknown</t>
+    <t>unknown</t>
   </si>
   <si>
     <t>brightfieldMicroscopy</t>
